--- a/docs/downloads/09/t11_sources_emprunt_marovoay_tous.xlsx
+++ b/docs/downloads/09/t11_sources_emprunt_marovoay_tous.xlsx
@@ -387,12 +387,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -405,12 +399,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -441,12 +429,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -477,12 +459,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -495,12 +471,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>2.3</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -531,12 +501,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>7</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -567,12 +531,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -585,12 +543,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>5.3</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -621,12 +573,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -657,12 +603,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -711,12 +651,6 @@
           <t>Usuriers</t>
         </is>
       </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20">
-        <v>13</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -746,12 +680,6 @@
         <is>
           <t>Autres</t>
         </is>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22">
-        <v>1.4</v>
       </c>
     </row>
     <row r="23">

--- a/docs/downloads/09/t11_sources_emprunt_marovoay_tous.xlsx
+++ b/docs/downloads/09/t11_sources_emprunt_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -403,7 +403,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -421,7 +421,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
